--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -118,7 +118,7 @@
     <t>Palco</t>
   </si>
   <si>
-    <t>70.05%</t>
+    <t>75.00%</t>
   </si>
   <si>
     <t>Zona del Recuerdo</t>
@@ -127,7 +127,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>4.95%</t>
+    <t>5.18%</t>
   </si>
 </sst>
 </file>
@@ -1083,7 +1083,7 @@
         <v>23</v>
       </c>
       <c r="I13" s="7">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>23</v>
@@ -1107,10 +1107,10 @@
         <v>364</v>
       </c>
       <c r="Q13" s="7">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="R13" s="7">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="S13" s="8" t="s">
         <v>35</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -97,7 +97,7 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>2.27%</t>
+    <t>2.54%</t>
   </si>
   <si>
     <t>Jardin</t>
@@ -124,7 +124,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>5.18%</t>
+    <t>5.26%</t>
   </si>
 </sst>
 </file>
@@ -817,7 +817,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
@@ -844,10 +844,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q9" s="6">
-        <v>2152</v>
+        <v>2146</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -19,7 +19,7 @@
     <t/>
   </si>
   <si>
-    <t>Juego Inaugural: Piratas vs Guereros</t>
+    <t>Juego Inaugural: Conspiradores vs Guerreros</t>
   </si>
   <si>
     <t>ZONA</t>
@@ -88,7 +88,7 @@
     <t>Central</t>
   </si>
   <si>
-    <t>4.57%</t>
+    <t>5.00%</t>
   </si>
   <si>
     <t>Discapacitados</t>
@@ -97,34 +97,31 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>2.54%</t>
+    <t>2.63%</t>
   </si>
   <si>
     <t>Jardin</t>
   </si>
   <si>
+    <t>NaN%</t>
+  </si>
+  <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>1.16%</t>
+    <t>1.10%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
   </si>
   <si>
-    <t>Palco</t>
-  </si>
-  <si>
-    <t>75.00%</t>
-  </si>
-  <si>
     <t>Zona del Recuerdo</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>5.26%</t>
+    <t>1.86%</t>
   </si>
 </sst>
 </file>
@@ -546,10 +543,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="41" customWidth="1"/>
+    <col min="1" max="1" width="48" customWidth="1"/>
     <col min="2" max="18" width="25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -690,7 +687,7 @@
         <v>24</v>
       </c>
       <c r="B7" s="6">
-        <v>1138</v>
+        <v>1120</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>22</v>
@@ -698,8 +695,8 @@
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>22</v>
+      <c r="E7" s="6">
+        <v>4</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -732,10 +729,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="Q7" s="6">
-        <v>1086</v>
+        <v>1064</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -823,7 +820,7 @@
         <v>22</v>
       </c>
       <c r="I9" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>22</v>
@@ -844,10 +841,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="Q9" s="6">
-        <v>2146</v>
+        <v>2144</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>28</v>
@@ -857,8 +854,8 @@
       <c r="A10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="6">
-        <v>2</v>
+      <c r="B10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
@@ -902,16 +899,16 @@
       <c r="P10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="6">
-        <v>2</v>
+      <c r="Q10" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
@@ -922,8 +919,8 @@
       <c r="D11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="6">
-        <v>1</v>
+      <c r="E11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F11" s="6" t="s">
         <v>22</v>
@@ -956,18 +953,18 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q11" s="6">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1023,10 +1020,10 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
-        <v>364</v>
+        <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>22</v>
@@ -1034,8 +1031,8 @@
       <c r="D13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="6">
-        <v>1</v>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
         <v>22</v>
@@ -1046,8 +1043,8 @@
       <c r="H13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="6">
-        <v>272</v>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>22</v>
@@ -1067,130 +1064,74 @@
       <c r="O13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P13" s="6">
-        <v>273</v>
+      <c r="P13" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="Q13" s="6">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="6">
-        <v>10</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q14" s="6">
-        <v>10</v>
-      </c>
-      <c r="R14" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="B14" s="7">
+        <f>SUM(B6:B13)</f>
+      </c>
+      <c r="C14" s="7">
+        <f>SUM(C6:C13)</f>
+      </c>
+      <c r="D14" s="7">
+        <f>SUM(D6:D13)</f>
+      </c>
+      <c r="E14" s="7">
+        <f>SUM(E6:E13)</f>
+      </c>
+      <c r="F14" s="7">
+        <f>SUM(F6:F13)</f>
+      </c>
+      <c r="G14" s="7">
+        <f>SUM(G6:G13)</f>
+      </c>
+      <c r="H14" s="7">
+        <f>SUM(H6:H13)</f>
+      </c>
+      <c r="I14" s="7">
+        <f>SUM(I6:I13)</f>
+      </c>
+      <c r="J14" s="7">
+        <f>SUM(J6:J13)</f>
+      </c>
+      <c r="K14" s="7">
+        <f>SUM(K6:K13)</f>
+      </c>
+      <c r="L14" s="7">
+        <f>SUM(L6:L13)</f>
+      </c>
+      <c r="M14" s="7">
+        <f>SUM(M6:M13)</f>
+      </c>
+      <c r="N14" s="7">
+        <f>SUM(N6:N13)</f>
+      </c>
+      <c r="O14" s="7">
+        <f>SUM(O6:O13)</f>
+      </c>
+      <c r="P14" s="7">
+        <f>SUM(P6:P13)</f>
+      </c>
+      <c r="Q14" s="7">
+        <f>SUM(Q6:Q13)</f>
+      </c>
+      <c r="R14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="7">
-        <f>SUM(B6:B14)</f>
-      </c>
-      <c r="C15" s="7">
-        <f>SUM(C6:C14)</f>
-      </c>
-      <c r="D15" s="7">
-        <f>SUM(D6:D14)</f>
-      </c>
-      <c r="E15" s="7">
-        <f>SUM(E6:E14)</f>
-      </c>
-      <c r="F15" s="7">
-        <f>SUM(F6:F14)</f>
-      </c>
-      <c r="G15" s="7">
-        <f>SUM(G6:G14)</f>
-      </c>
-      <c r="H15" s="7">
-        <f>SUM(H6:H14)</f>
-      </c>
-      <c r="I15" s="7">
-        <f>SUM(I6:I14)</f>
-      </c>
-      <c r="J15" s="7">
-        <f>SUM(J6:J14)</f>
-      </c>
-      <c r="K15" s="7">
-        <f>SUM(K6:K14)</f>
-      </c>
-      <c r="L15" s="7">
-        <f>SUM(L6:L14)</f>
-      </c>
-      <c r="M15" s="7">
-        <f>SUM(M6:M14)</f>
-      </c>
-      <c r="N15" s="7">
-        <f>SUM(N6:N14)</f>
-      </c>
-      <c r="O15" s="7">
-        <f>SUM(O6:O14)</f>
-      </c>
-      <c r="P15" s="7">
-        <f>SUM(P6:P14)</f>
-      </c>
-      <c r="Q15" s="7">
-        <f>SUM(Q6:Q14)</f>
-      </c>
-      <c r="R15" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
     </row>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="38">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,22 +82,25 @@
     <t>-</t>
   </si>
   <si>
+    <t>0.38%</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>16.43%</t>
+  </si>
+  <si>
+    <t>Discapacitados</t>
+  </si>
+  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t>5.00%</t>
-  </si>
-  <si>
-    <t>Discapacitados</t>
-  </si>
-  <si>
     <t>Dogout</t>
   </si>
   <si>
-    <t>2.63%</t>
+    <t>6.77%</t>
   </si>
   <si>
     <t>Jardin</t>
@@ -109,7 +112,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>1.10%</t>
+    <t>2.42%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -121,7 +124,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>1.86%</t>
+    <t>5.26%</t>
   </si>
 </sst>
 </file>
@@ -633,8 +636,8 @@
       <c r="B6" s="6">
         <v>1062</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>22</v>
+      <c r="C6" s="6">
+        <v>4</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -672,11 +675,11 @@
       <c r="O6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="6" t="s">
-        <v>22</v>
+      <c r="P6" s="6">
+        <v>4</v>
       </c>
       <c r="Q6" s="6">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -689,8 +692,8 @@
       <c r="B7" s="6">
         <v>1120</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>22</v>
+      <c r="C7" s="6">
+        <v>128</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -729,10 +732,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="Q7" s="6">
-        <v>1064</v>
+        <v>936</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -791,18 +794,18 @@
         <v>36</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="6">
         <v>2202</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>22</v>
+      <c r="C9" s="6">
+        <v>91</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -841,18 +844,18 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>58</v>
+        <v>149</v>
       </c>
       <c r="Q9" s="6">
-        <v>2144</v>
+        <v>2053</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>22</v>
@@ -903,18 +906,18 @@
         <v>22</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>22</v>
+      <c r="C11" s="6">
+        <v>25</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -953,18 +956,18 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="Q11" s="6">
-        <v>1881</v>
+        <v>1856</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1015,12 +1018,12 @@
         <v>945</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1071,12 +1074,12 @@
         <v>10</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1127,7 +1130,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -88,7 +88,7 @@
     <t>Central</t>
   </si>
   <si>
-    <t>16.43%</t>
+    <t>27.50%</t>
   </si>
   <si>
     <t>Discapacitados</t>
@@ -100,7 +100,7 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>6.77%</t>
+    <t>12.08%</t>
   </si>
   <si>
     <t>Jardin</t>
@@ -112,7 +112,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>2.42%</t>
+    <t>2.84%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -124,7 +124,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>5.26%</t>
+    <t>8.68%</t>
   </si>
 </sst>
 </file>
@@ -693,7 +693,7 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="G7" s="6">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>22</v>
@@ -732,10 +732,10 @@
         <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>184</v>
+        <v>308</v>
       </c>
       <c r="Q7" s="6">
-        <v>936</v>
+        <v>812</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -805,7 +805,7 @@
         <v>2202</v>
       </c>
       <c r="C9" s="6">
-        <v>91</v>
+        <v>206</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -817,7 +817,7 @@
         <v>22</v>
       </c>
       <c r="G9" s="6">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>22</v>
@@ -844,10 +844,10 @@
         <v>22</v>
       </c>
       <c r="P9" s="6">
-        <v>149</v>
+        <v>266</v>
       </c>
       <c r="Q9" s="6">
-        <v>2053</v>
+        <v>1936</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -917,7 +917,7 @@
         <v>1902</v>
       </c>
       <c r="C11" s="6">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -956,10 +956,10 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="6">
-        <v>1856</v>
+        <v>1848</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>0.38%</t>
+    <t>0.66%</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>27.50%</t>
+    <t>56.79%</t>
   </si>
   <si>
     <t>Discapacitados</t>
@@ -100,19 +100,16 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>12.08%</t>
+    <t>29.06%</t>
   </si>
   <si>
     <t>Jardin</t>
   </si>
   <si>
-    <t>NaN%</t>
-  </si>
-  <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>2.84%</t>
+    <t>11.20%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -124,7 +121,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>8.68%</t>
+    <t>20.55%</t>
   </si>
 </sst>
 </file>
@@ -660,8 +657,8 @@
       <c r="J6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>22</v>
+      <c r="K6" s="6">
+        <v>3</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>22</v>
@@ -676,10 +673,10 @@
         <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="6">
-        <v>1058</v>
+        <v>1055</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -716,26 +713,26 @@
       <c r="J7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>22</v>
+      <c r="K7" s="6">
+        <v>202</v>
+      </c>
+      <c r="L7" s="6">
+        <v>100</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O7" s="6" t="s">
-        <v>22</v>
+      <c r="N7" s="6">
+        <v>24</v>
+      </c>
+      <c r="O7" s="6">
+        <v>2</v>
       </c>
       <c r="P7" s="6">
-        <v>308</v>
+        <v>636</v>
       </c>
       <c r="Q7" s="6">
-        <v>812</v>
+        <v>484</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -828,8 +825,8 @@
       <c r="J9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>22</v>
+      <c r="K9" s="6">
+        <v>226</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -837,17 +834,17 @@
       <c r="M9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O9" s="6" t="s">
-        <v>22</v>
+      <c r="N9" s="6">
+        <v>143</v>
+      </c>
+      <c r="O9" s="6">
+        <v>5</v>
       </c>
       <c r="P9" s="6">
-        <v>266</v>
+        <v>640</v>
       </c>
       <c r="Q9" s="6">
-        <v>1936</v>
+        <v>1562</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -857,8 +854,8 @@
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>22</v>
+      <c r="B10" s="6">
+        <v>2</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
@@ -902,16 +899,16 @@
       <c r="P10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="6" t="s">
-        <v>22</v>
+      <c r="Q10" s="6">
+        <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
@@ -940,8 +937,8 @@
       <c r="J11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>22</v>
+      <c r="K11" s="6">
+        <v>17</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>22</v>
@@ -949,25 +946,25 @@
       <c r="M11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O11" s="6" t="s">
-        <v>22</v>
+      <c r="N11" s="6">
+        <v>140</v>
+      </c>
+      <c r="O11" s="6">
+        <v>2</v>
       </c>
       <c r="P11" s="6">
-        <v>54</v>
+        <v>213</v>
       </c>
       <c r="Q11" s="6">
-        <v>1848</v>
+        <v>1689</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1023,7 +1020,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1079,7 +1076,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1130,7 +1127,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="37">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>0.66%</t>
+    <t>11.39%</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>56.79%</t>
+    <t>99.82%</t>
   </si>
   <si>
     <t>Discapacitados</t>
@@ -100,7 +100,7 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>29.06%</t>
+    <t>99.73%</t>
   </si>
   <si>
     <t>Jardin</t>
@@ -109,7 +109,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>11.20%</t>
+    <t>53.21%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -121,7 +121,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>20.55%</t>
+    <t>61.09%</t>
   </si>
 </sst>
 </file>
@@ -634,7 +634,7 @@
         <v>1062</v>
       </c>
       <c r="C6" s="6">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -658,7 +658,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L6" s="6" t="s">
         <v>22</v>
@@ -669,14 +669,14 @@
       <c r="N6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>22</v>
+      <c r="O6" s="6">
+        <v>6</v>
       </c>
       <c r="P6" s="6">
-        <v>7</v>
+        <v>121</v>
       </c>
       <c r="Q6" s="6">
-        <v>1055</v>
+        <v>941</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -690,13 +690,13 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>243</v>
+        <v>606</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="E7" s="6">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>22</v>
@@ -714,7 +714,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="6">
-        <v>202</v>
+        <v>294</v>
       </c>
       <c r="L7" s="6">
         <v>100</v>
@@ -723,16 +723,16 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="O7" s="6">
+        <v>1</v>
+      </c>
+      <c r="P7" s="6">
+        <v>1118</v>
+      </c>
+      <c r="Q7" s="6">
         <v>2</v>
-      </c>
-      <c r="P7" s="6">
-        <v>636</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>484</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -802,7 +802,7 @@
         <v>2202</v>
       </c>
       <c r="C9" s="6">
-        <v>206</v>
+        <v>1564</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -826,7 +826,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="6">
-        <v>226</v>
+        <v>342</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>22</v>
@@ -835,16 +835,16 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>143</v>
+        <v>223</v>
       </c>
       <c r="O9" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P9" s="6">
-        <v>640</v>
+        <v>2196</v>
       </c>
       <c r="Q9" s="6">
-        <v>1562</v>
+        <v>6</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -914,7 +914,7 @@
         <v>1902</v>
       </c>
       <c r="C11" s="6">
-        <v>33</v>
+        <v>760</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -938,7 +938,7 @@
         <v>22</v>
       </c>
       <c r="K11" s="6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>22</v>
@@ -950,13 +950,13 @@
         <v>140</v>
       </c>
       <c r="O11" s="6">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="P11" s="6">
-        <v>213</v>
+        <v>1012</v>
       </c>
       <c r="Q11" s="6">
-        <v>1689</v>
+        <v>890</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>32</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="36">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,13 +82,13 @@
     <t>-</t>
   </si>
   <si>
-    <t>11.39%</t>
+    <t>27.97%</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>99.82%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Discapacitados</t>
@@ -100,16 +100,13 @@
     <t>Dogout</t>
   </si>
   <si>
-    <t>99.73%</t>
-  </si>
-  <si>
     <t>Jardin</t>
   </si>
   <si>
     <t>Lateral</t>
   </si>
   <si>
-    <t>53.21%</t>
+    <t>92.90%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -121,7 +118,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>61.09%</t>
+    <t>73.99%</t>
   </si>
 </sst>
 </file>
@@ -634,7 +631,7 @@
         <v>1062</v>
       </c>
       <c r="C6" s="6">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -670,13 +667,13 @@
         <v>22</v>
       </c>
       <c r="O6" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P6" s="6">
-        <v>121</v>
+        <v>297</v>
       </c>
       <c r="Q6" s="6">
-        <v>941</v>
+        <v>765</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -690,7 +687,7 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -725,14 +722,14 @@
       <c r="N7" s="6">
         <v>46</v>
       </c>
-      <c r="O7" s="6">
-        <v>1</v>
+      <c r="O7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P7" s="6">
-        <v>1118</v>
-      </c>
-      <c r="Q7" s="6">
-        <v>2</v>
+        <v>1120</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>25</v>
@@ -802,7 +799,7 @@
         <v>2202</v>
       </c>
       <c r="C9" s="6">
-        <v>1564</v>
+        <v>1577</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -835,24 +832,24 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O9" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="P9" s="6">
-        <v>2196</v>
-      </c>
-      <c r="Q9" s="6">
-        <v>6</v>
+        <v>2202</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B10" s="6">
         <v>2</v>
@@ -908,13 +905,13 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
       </c>
       <c r="C11" s="6">
-        <v>760</v>
+        <v>1544</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -932,7 +929,7 @@
         <v>22</v>
       </c>
       <c r="I11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>22</v>
@@ -950,21 +947,21 @@
         <v>140</v>
       </c>
       <c r="O11" s="6">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="P11" s="6">
-        <v>1012</v>
+        <v>1767</v>
       </c>
       <c r="Q11" s="6">
-        <v>890</v>
+        <v>135</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1020,7 +1017,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1076,7 +1073,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1127,7 +1124,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="36">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,7 +82,7 @@
     <t>-</t>
   </si>
   <si>
-    <t>27.97%</t>
+    <t>73.26%</t>
   </si>
   <si>
     <t>Central</t>
@@ -106,7 +106,7 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>92.90%</t>
+    <t>99.68%</t>
   </si>
   <si>
     <t>Lateral Superior</t>
@@ -118,7 +118,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>73.99%</t>
+    <t>82.37%</t>
   </si>
 </sst>
 </file>
@@ -631,7 +631,7 @@
         <v>1062</v>
       </c>
       <c r="C6" s="6">
-        <v>288</v>
+        <v>749</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -663,17 +663,17 @@
       <c r="M6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="6" t="s">
-        <v>22</v>
+      <c r="N6" s="6">
+        <v>10</v>
       </c>
       <c r="O6" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P6" s="6">
-        <v>297</v>
+        <v>778</v>
       </c>
       <c r="Q6" s="6">
-        <v>765</v>
+        <v>284</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -687,7 +687,7 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -720,7 +720,7 @@
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -799,7 +799,7 @@
         <v>2202</v>
       </c>
       <c r="C9" s="6">
-        <v>1577</v>
+        <v>1651</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -832,10 +832,10 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>221</v>
-      </c>
-      <c r="O9" s="6">
-        <v>2</v>
+        <v>149</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P9" s="6">
         <v>2202</v>
@@ -911,7 +911,7 @@
         <v>1902</v>
       </c>
       <c r="C11" s="6">
-        <v>1544</v>
+        <v>1709</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -946,14 +946,14 @@
       <c r="N11" s="6">
         <v>140</v>
       </c>
-      <c r="O11" s="6">
-        <v>36</v>
+      <c r="O11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>1767</v>
+        <v>1896</v>
       </c>
       <c r="Q11" s="6">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>31</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="34">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -82,15 +82,12 @@
     <t>-</t>
   </si>
   <si>
-    <t>73.26%</t>
+    <t>100.00%</t>
   </si>
   <si>
     <t>Central</t>
   </si>
   <si>
-    <t>100.00%</t>
-  </si>
-  <si>
     <t>Discapacitados</t>
   </si>
   <si>
@@ -106,9 +103,6 @@
     <t>Lateral</t>
   </si>
   <si>
-    <t>99.68%</t>
-  </si>
-  <si>
     <t>Lateral Superior</t>
   </si>
   <si>
@@ -118,7 +112,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>82.37%</t>
+    <t>86.36%</t>
   </si>
 </sst>
 </file>
@@ -631,7 +625,7 @@
         <v>1062</v>
       </c>
       <c r="C6" s="6">
-        <v>749</v>
+        <v>1047</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>22</v>
@@ -666,14 +660,14 @@
       <c r="N6" s="6">
         <v>10</v>
       </c>
-      <c r="O6" s="6">
-        <v>14</v>
+      <c r="O6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="P6" s="6">
-        <v>778</v>
-      </c>
-      <c r="Q6" s="6">
-        <v>284</v>
+        <v>1062</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>23</v>
@@ -687,7 +681,7 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -714,13 +708,13 @@
         <v>294</v>
       </c>
       <c r="L7" s="6">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -732,12 +726,12 @@
         <v>22</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>36</v>
@@ -788,12 +782,12 @@
         <v>36</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B9" s="6">
         <v>2202</v>
@@ -844,12 +838,12 @@
         <v>22</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B10" s="6">
         <v>2</v>
@@ -900,18 +894,18 @@
         <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
       </c>
       <c r="C11" s="6">
-        <v>1709</v>
+        <v>1715</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>22</v>
@@ -950,18 +944,18 @@
         <v>22</v>
       </c>
       <c r="P11" s="6">
-        <v>1896</v>
-      </c>
-      <c r="Q11" s="6">
-        <v>6</v>
+        <v>1902</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1012,12 +1006,12 @@
         <v>945</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1068,12 +1062,12 @@
         <v>10</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1124,7 +1118,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -708,13 +708,13 @@
         <v>294</v>
       </c>
       <c r="L7" s="6">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -793,7 +793,7 @@
         <v>2202</v>
       </c>
       <c r="C9" s="6">
-        <v>1651</v>
+        <v>1657</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>22</v>
@@ -826,7 +826,7 @@
         <v>22</v>
       </c>
       <c r="N9" s="6">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>22</v>

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="35">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -91,15 +91,18 @@
     <t>Discapacitados</t>
   </si>
   <si>
+    <t>11.11%</t>
+  </si>
+  <si>
+    <t>Dogout</t>
+  </si>
+  <si>
+    <t>Jardin</t>
+  </si>
+  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Dogout</t>
-  </si>
-  <si>
-    <t>Jardin</t>
-  </si>
-  <si>
     <t>Lateral</t>
   </si>
   <si>
@@ -112,7 +115,7 @@
     <t>TOTALES</t>
   </si>
   <si>
-    <t>86.36%</t>
+    <t>86.41%</t>
   </si>
 </sst>
 </file>
@@ -681,7 +684,7 @@
         <v>1120</v>
       </c>
       <c r="C7" s="6">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>22</v>
@@ -708,13 +711,13 @@
         <v>294</v>
       </c>
       <c r="L7" s="6">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N7" s="6">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>22</v>
@@ -736,8 +739,8 @@
       <c r="B8" s="6">
         <v>36</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>22</v>
+      <c r="C8" s="6">
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -775,11 +778,11 @@
       <c r="O8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="6" t="s">
-        <v>22</v>
+      <c r="P8" s="6">
+        <v>4</v>
       </c>
       <c r="Q8" s="6">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>26</v>
@@ -894,12 +897,12 @@
         <v>2</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6">
         <v>1902</v>
@@ -931,14 +934,14 @@
       <c r="K11" s="6">
         <v>25</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>22</v>
+      <c r="L11" s="6">
+        <v>50</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="6">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>22</v>
@@ -955,7 +958,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>945</v>
@@ -1006,12 +1009,12 @@
         <v>945</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6">
         <v>10</v>
@@ -1062,12 +1065,12 @@
         <v>10</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1118,7 +1121,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">

--- a/data/asistencia/Guerreros 2026.xlsx
+++ b/data/asistencia/Guerreros 2026.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="36">
   <si>
     <t>Reporte de disponibilidad por zona</t>
   </si>
@@ -91,7 +91,7 @@
     <t>Discapacitados</t>
   </si>
   <si>
-    <t>11.11%</t>
+    <t>38.89%</t>
   </si>
   <si>
     <t>Dogout</t>
@@ -100,22 +100,25 @@
     <t>Jardin</t>
   </si>
   <si>
+    <t>37.66%</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+  </si>
+  <si>
+    <t>Lateral Superior</t>
+  </si>
+  <si>
     <t>0.00%</t>
   </si>
   <si>
-    <t>Lateral</t>
-  </si>
-  <si>
-    <t>Lateral Superior</t>
-  </si>
-  <si>
     <t>Zona del Recuerdo</t>
   </si>
   <si>
     <t>TOTALES</t>
   </si>
   <si>
-    <t>86.41%</t>
+    <t>75.60%</t>
   </si>
 </sst>
 </file>
@@ -740,7 +743,7 @@
         <v>36</v>
       </c>
       <c r="C8" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>22</v>
@@ -779,10 +782,10 @@
         <v>22</v>
       </c>
       <c r="P8" s="6">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q8" s="6">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>26</v>
@@ -849,7 +852,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="6">
-        <v>2</v>
+        <v>531</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>22</v>
@@ -878,8 +881,8 @@
       <c r="K10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>22</v>
+      <c r="L10" s="6">
+        <v>200</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>22</v>
@@ -890,11 +893,11 @@
       <c r="O10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="6" t="s">
-        <v>22</v>
+      <c r="P10" s="6">
+        <v>200</v>
       </c>
       <c r="Q10" s="6">
-        <v>2</v>
+        <v>331</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1009,68 +1012,68 @@
         <v>945</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="6">
+        <v>800</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q13" s="6">
+        <v>800</v>
+      </c>
+      <c r="R13" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="6">
-        <v>10</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="O13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>10</v>
-      </c>
-      <c r="R13" s="6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="7">
         <f>SUM(B6:B13)</f>
@@ -1121,7 +1124,7 @@
         <f>SUM(Q6:Q13)</f>
       </c>
       <c r="R14" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
